--- a/ch_05/ch_05_solution.xlsx
+++ b/ch_05/ch_05_solution.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_05_statistical_testing_inference\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{941EA154-0954-4025-B5A5-832FECC9DBBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B62E5C87-FECC-4F76-9C62-ED0F69C35806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1297,13 +1297,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>694267</xdr:colOff>
       <xdr:row>55</xdr:row>
-      <xdr:rowOff>135467</xdr:rowOff>
+      <xdr:rowOff>135466</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>585789</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>100013</xdr:colOff>
       <xdr:row>67</xdr:row>
-      <xdr:rowOff>154617</xdr:rowOff>
+      <xdr:rowOff>1524655</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1331,8 +1331,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="694267" y="10147300"/>
-          <a:ext cx="3272367" cy="2203550"/>
+          <a:off x="694267" y="10089091"/>
+          <a:ext cx="5273146" cy="3560889"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1346,13 +1346,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>21168</xdr:colOff>
       <xdr:row>77</xdr:row>
-      <xdr:rowOff>118533</xdr:rowOff>
+      <xdr:rowOff>118532</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>441355</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>127001</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>158234</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1380,8 +1380,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1236135" y="14135100"/>
-          <a:ext cx="3802620" cy="2556934"/>
+          <a:off x="859368" y="15439495"/>
+          <a:ext cx="6236757" cy="4202127"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -14196,6 +14196,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
+    <row r="68" spans="1:4" ht="123.4" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71" t="str" cm="1">
         <f t="array" ref="A71:D73">_xlfn._xlws.PY(13,0)</f>
